--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.62767293498644</v>
+        <v>11.8019968519353</v>
       </c>
       <c r="D2" t="n">
-        <v>71.78821489906335</v>
+        <v>11.66558492109779</v>
       </c>
       <c r="E2" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F2" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.48715377865931</v>
+        <v>8.854162489032138</v>
       </c>
       <c r="D3" t="n">
-        <v>54.98978609075718</v>
+        <v>8.935840239748043</v>
       </c>
       <c r="E3" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F3" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.7954956137693</v>
+        <v>8.741768037237513</v>
       </c>
       <c r="D4" t="n">
-        <v>55.19961239977636</v>
+        <v>8.969937014963659</v>
       </c>
       <c r="E4" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F4" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.56982541355054</v>
+        <v>3.667596629701962</v>
       </c>
       <c r="D5" t="n">
-        <v>23.50293512800799</v>
+        <v>3.819226958301299</v>
       </c>
       <c r="E5" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F5" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.64210536387497</v>
+        <v>10.34184212162968</v>
       </c>
       <c r="D6" t="n">
-        <v>65.28070405755928</v>
+        <v>10.60811440935338</v>
       </c>
       <c r="E6" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F6" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.87978102672304</v>
+        <v>5.342964416842494</v>
       </c>
       <c r="D7" t="n">
-        <v>25.12468905280222</v>
+        <v>4.082761971080362</v>
       </c>
       <c r="E7" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F7" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>74.86585825978324</v>
+        <v>12.16570196721478</v>
       </c>
       <c r="D8" t="n">
-        <v>76.18271095817636</v>
+        <v>12.37969053070366</v>
       </c>
       <c r="E8" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F8" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.63399051228246</v>
+        <v>8.715523458245899</v>
       </c>
       <c r="D9" t="n">
-        <v>48.86972477925367</v>
+        <v>7.941330276628721</v>
       </c>
       <c r="E9" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F9" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.66507511274505</v>
+        <v>1.73307470582107</v>
       </c>
       <c r="D10" t="n">
-        <v>15.95305613354382</v>
+        <v>2.59237162170087</v>
       </c>
       <c r="E10" t="n">
-        <v>20.93346343004031</v>
+        <v>3.40168780738155</v>
       </c>
       <c r="F10" t="n">
-        <v>20.83786414397228</v>
+        <v>3.386152923395494</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
